--- a/chapters/08/guides/AIHE-RG05/edit/xlsx/AIHE-RG05_register.xlsx
+++ b/chapters/08/guides/AIHE-RG05/edit/xlsx/AIHE-RG05_register.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Ra3d74907ff1a4c63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Register" sheetId="2" r:id="R25cccd7bb4694718"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local Copy" sheetId="3" r:id="Rb3d3cb583eae47a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R5ae989ef0a974685"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Register" sheetId="2" r:id="R5ac66d4265014091"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local Copy" sheetId="3" r:id="R04f7adcc917b4e62"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -189,14 +189,10 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
-      <x:alignment/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyAlignment="1">
@@ -306,9 +302,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment/>
-    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -660,10 +654,8 @@
           <x:t xml:space="preserve">Additional alignment</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1, 6-9, 12, 15</x:t>
-        </x:is>
+      <x:c r="B5" s="27" t="str">
+        <x:v>1, 6-9, 12</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
